--- a/frontend/public/master_supervisor_users_test_data.xlsx
+++ b/frontend/public/master_supervisor_users_test_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,143 +418,109 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>prabesh.bhattarai@pcampus.edu.np</v>
+        <v>dr..dineshkoirala@pcampus.edu.np</v>
       </c>
       <c r="B2" t="str">
-        <v>subesh</v>
+        <v>Test@123</v>
       </c>
       <c r="C2" t="str">
-        <v>Prabesh</v>
+        <v>Dr.</v>
       </c>
       <c r="D2" t="str">
-        <v>Bhattarai</v>
+        <v>Dinesh Koirala</v>
       </c>
       <c r="E2" t="str">
-        <v>Assoc. Prof. Dr.</v>
+        <v>Prof.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ramesh.sharma@pcampus.edu.np</v>
+        <v>prof..dr.meenashrestha@pcampus.edu.np</v>
       </c>
       <c r="B3" t="str">
-        <v>subesh</v>
+        <v>Test@123</v>
       </c>
       <c r="C3" t="str">
-        <v>Ramesh</v>
+        <v>Prof.</v>
       </c>
       <c r="D3" t="str">
-        <v>Sharma</v>
+        <v>Dr. Meena Shrestha</v>
       </c>
       <c r="E3" t="str">
-        <v>Assoc. Prof.</v>
+        <v>Assoc.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>anita.gurung@pcampus.edu.np</v>
+        <v>kiran.adhikari@pcampus.edu.np</v>
       </c>
       <c r="B4" t="str">
-        <v>subesh</v>
+        <v>Test@123</v>
       </c>
       <c r="C4" t="str">
-        <v>Anita</v>
+        <v>Kiran</v>
       </c>
       <c r="D4" t="str">
-        <v>Gurung</v>
+        <v>Adhikari</v>
       </c>
       <c r="E4" t="str">
-        <v>Asst. Prof. Dr.</v>
+        <v>Dr.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>bishnu.tamang@pcampus.edu.np</v>
+        <v>prof..dr.gyanendrathapa@pcampus.edu.np</v>
       </c>
       <c r="B5" t="str">
-        <v>subesh</v>
+        <v>Test@123</v>
       </c>
       <c r="C5" t="str">
-        <v>Bishnu</v>
+        <v>Prof.</v>
       </c>
       <c r="D5" t="str">
-        <v>Tamang</v>
+        <v>Dr. Gyanendra Thapa</v>
       </c>
       <c r="E5" t="str">
-        <v>Asst. Prof.</v>
+        <v>Assoc.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>sagar.acharya@pcampus.edu.np</v>
+        <v>nilima.joshi@pcampus.edu.np</v>
       </c>
       <c r="B6" t="str">
-        <v>subesh</v>
+        <v>Test@123</v>
       </c>
       <c r="C6" t="str">
-        <v>Sagar</v>
+        <v>Nilima</v>
       </c>
       <c r="D6" t="str">
-        <v>Acharya</v>
+        <v>Joshi</v>
       </c>
       <c r="E6" t="str">
-        <v>Prof. Dr.</v>
+        <v>Dr.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>maya.khadka@pcampus.edu.np</v>
+        <v>dr..rajupoudel@pcampus.edu.np</v>
       </c>
       <c r="B7" t="str">
-        <v>subesh</v>
+        <v>Test@123</v>
       </c>
       <c r="C7" t="str">
-        <v>Maya</v>
+        <v>Dr.</v>
       </c>
       <c r="D7" t="str">
-        <v>Khadka</v>
+        <v>Raju Poudel</v>
       </c>
       <c r="E7" t="str">
-        <v>Asst. Prof. Dr.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>rajendra.neupane@pcampus.edu.np</v>
-      </c>
-      <c r="B8" t="str">
-        <v>subesh</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Rajendra</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Neupane</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Assoc. Prof. Dr.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>sarita.poudel@pcampus.edu.np</v>
-      </c>
-      <c r="B9" t="str">
-        <v>subesh</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Sarita</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Poudel</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Asst. Prof.</v>
+        <v>Prof.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/frontend/public/master_supervisor_users_test_data.xlsx
+++ b/frontend/public/master_supervisor_users_test_data.xlsx
@@ -418,36 +418,36 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>dr..dineshkoirala@pcampus.edu.np</v>
+        <v>dinesh.koirala@pcampus.edu.np</v>
       </c>
       <c r="B2" t="str">
         <v>Test@123</v>
       </c>
       <c r="C2" t="str">
-        <v>Dr.</v>
+        <v>Dinesh</v>
       </c>
       <c r="D2" t="str">
-        <v>Dinesh Koirala</v>
+        <v>Koirala</v>
       </c>
       <c r="E2" t="str">
-        <v>Prof.</v>
+        <v>Prof. Dr.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>prof..dr.meenashrestha@pcampus.edu.np</v>
+        <v>meena.shrestha@pcampus.edu.np</v>
       </c>
       <c r="B3" t="str">
         <v>Test@123</v>
       </c>
       <c r="C3" t="str">
-        <v>Prof.</v>
+        <v>Meena</v>
       </c>
       <c r="D3" t="str">
-        <v>Dr. Meena Shrestha</v>
+        <v>Shrestha</v>
       </c>
       <c r="E3" t="str">
-        <v>Assoc.</v>
+        <v>Assoc. Prof. Dr.</v>
       </c>
     </row>
     <row r="4">
@@ -469,19 +469,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>prof..dr.gyanendrathapa@pcampus.edu.np</v>
+        <v>gyanendra.thapa@pcampus.edu.np</v>
       </c>
       <c r="B5" t="str">
         <v>Test@123</v>
       </c>
       <c r="C5" t="str">
-        <v>Prof.</v>
+        <v>Gyanendra</v>
       </c>
       <c r="D5" t="str">
-        <v>Dr. Gyanendra Thapa</v>
+        <v>Thapa</v>
       </c>
       <c r="E5" t="str">
-        <v>Assoc.</v>
+        <v>Assoc. Prof. Dr.</v>
       </c>
     </row>
     <row r="6">
@@ -503,19 +503,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>dr..rajupoudel@pcampus.edu.np</v>
+        <v>raju.poudel@pcampus.edu.np</v>
       </c>
       <c r="B7" t="str">
         <v>Test@123</v>
       </c>
       <c r="C7" t="str">
-        <v>Dr.</v>
+        <v>Raju</v>
       </c>
       <c r="D7" t="str">
-        <v>Raju Poudel</v>
+        <v>Poudel</v>
       </c>
       <c r="E7" t="str">
-        <v>Prof.</v>
+        <v>Prof. Dr.</v>
       </c>
     </row>
   </sheetData>
